--- a/Assets/Excel/EquipmentSlotRatio.xlsx
+++ b/Assets/Excel/EquipmentSlotRatio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenBox\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4B182AA-CF02-4373-A35A-E33FDAD6F354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2FFD5E3-AEE6-418C-8CB2-BA6B217A0650}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="3270" windowWidth="21645" windowHeight="13440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32040" yWindow="2295" windowWidth="21645" windowHeight="13440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -473,7 +473,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -490,7 +490,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B5">
         <v>0.8</v>
@@ -507,7 +507,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B6">
         <v>0.75</v>
@@ -524,7 +524,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B7">
         <v>0.9</v>
@@ -541,7 +541,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B8">
         <v>0.8</v>
@@ -558,7 +558,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B9">
         <v>0.75</v>
@@ -575,7 +575,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B10">
         <v>0.9</v>
@@ -592,7 +592,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B11">
         <v>0.8</v>
@@ -609,7 +609,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B12">
         <v>0.75</v>
@@ -626,7 +626,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B13">
         <v>0.8</v>
@@ -643,7 +643,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B14">
         <v>0.75</v>
@@ -660,7 +660,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B15">
         <v>0.9</v>

--- a/Assets/Excel/EquipmentSlotRatio.xlsx
+++ b/Assets/Excel/EquipmentSlotRatio.xlsx
@@ -8,24 +8,33 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenBox\Assets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2FFD5E3-AEE6-418C-8CB2-BA6B217A0650}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37BA863B-CA9A-46AD-A264-89B17BFB0EAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32040" yWindow="2295" windowWidth="21645" windowHeight="13440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4080" yWindow="1590" windowWidth="21645" windowHeight="13440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="24">
   <si>
     <t>ID索引</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -68,6 +77,54 @@
   </si>
   <si>
     <t>Agility</t>
+  </si>
+  <si>
+    <t>暴击</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>反击</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>连击</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>闪避</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>击晕</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>吸血</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CritRate</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CounterRate</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ComboRate</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DodgeRate</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>StunRate</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>LifeStealRate</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -99,7 +156,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -109,6 +166,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -125,7 +194,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -137,6 +206,12 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -417,10 +492,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:Q15"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -436,8 +511,50 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="1" t="str">
+        <f>"抗"&amp;F1</f>
+        <v>抗暴击</v>
+      </c>
+      <c r="M1" s="1" t="str">
+        <f>"抗"&amp;G1</f>
+        <v>抗反击</v>
+      </c>
+      <c r="N1" s="1" t="str">
+        <f>"抗"&amp;H1</f>
+        <v>抗连击</v>
+      </c>
+      <c r="O1" s="1" t="str">
+        <f>"抗"&amp;I1</f>
+        <v>抗闪避</v>
+      </c>
+      <c r="P1" s="1" t="str">
+        <f>"抗"&amp;J1</f>
+        <v>抗击晕</v>
+      </c>
+      <c r="Q1" s="1" t="str">
+        <f>"抗"&amp;K1</f>
+        <v>抗吸血</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -453,8 +570,44 @@
       <c r="E2" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>7</v>
       </c>
@@ -470,8 +623,50 @@
       <c r="E3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L3" s="6" t="str">
+        <f>"Anti"&amp;F3</f>
+        <v>AntiCritRate</v>
+      </c>
+      <c r="M3" s="6" t="str">
+        <f>"Anti"&amp;G3</f>
+        <v>AntiCounterRate</v>
+      </c>
+      <c r="N3" s="6" t="str">
+        <f>"Anti"&amp;H3</f>
+        <v>AntiComboRate</v>
+      </c>
+      <c r="O3" s="6" t="str">
+        <f>"Anti"&amp;I3</f>
+        <v>AntiDodgeRate</v>
+      </c>
+      <c r="P3" s="6" t="str">
+        <f>"Anti"&amp;J3</f>
+        <v>AntiStunRate</v>
+      </c>
+      <c r="Q3" s="6" t="str">
+        <f>"Anti"&amp;K3</f>
+        <v>AntiLifeStealRate</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>0</v>
       </c>
@@ -487,8 +682,44 @@
       <c r="E4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+      <c r="N4">
+        <v>1</v>
+      </c>
+      <c r="O4">
+        <v>1</v>
+      </c>
+      <c r="P4">
+        <v>1</v>
+      </c>
+      <c r="Q4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>1</v>
       </c>
@@ -504,8 +735,44 @@
       <c r="E5">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F5">
+        <v>0.8</v>
+      </c>
+      <c r="G5">
+        <v>0.8</v>
+      </c>
+      <c r="H5">
+        <v>0.8</v>
+      </c>
+      <c r="I5">
+        <v>0.8</v>
+      </c>
+      <c r="J5">
+        <v>0.8</v>
+      </c>
+      <c r="K5">
+        <v>0.8</v>
+      </c>
+      <c r="L5">
+        <v>0.8</v>
+      </c>
+      <c r="M5">
+        <v>0.8</v>
+      </c>
+      <c r="N5">
+        <v>0.8</v>
+      </c>
+      <c r="O5">
+        <v>0.8</v>
+      </c>
+      <c r="P5">
+        <v>0.8</v>
+      </c>
+      <c r="Q5">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>2</v>
       </c>
@@ -521,8 +788,44 @@
       <c r="E6">
         <v>0.75</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F6">
+        <v>0.75</v>
+      </c>
+      <c r="G6">
+        <v>0.75</v>
+      </c>
+      <c r="H6">
+        <v>0.75</v>
+      </c>
+      <c r="I6">
+        <v>0.75</v>
+      </c>
+      <c r="J6">
+        <v>0.75</v>
+      </c>
+      <c r="K6">
+        <v>0.75</v>
+      </c>
+      <c r="L6">
+        <v>0.75</v>
+      </c>
+      <c r="M6">
+        <v>0.75</v>
+      </c>
+      <c r="N6">
+        <v>0.75</v>
+      </c>
+      <c r="O6">
+        <v>0.75</v>
+      </c>
+      <c r="P6">
+        <v>0.75</v>
+      </c>
+      <c r="Q6">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>3</v>
       </c>
@@ -538,8 +841,44 @@
       <c r="E7">
         <v>0.9</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F7">
+        <v>0.9</v>
+      </c>
+      <c r="G7">
+        <v>0.9</v>
+      </c>
+      <c r="H7">
+        <v>0.9</v>
+      </c>
+      <c r="I7">
+        <v>0.9</v>
+      </c>
+      <c r="J7">
+        <v>0.9</v>
+      </c>
+      <c r="K7">
+        <v>0.9</v>
+      </c>
+      <c r="L7">
+        <v>0.9</v>
+      </c>
+      <c r="M7">
+        <v>0.9</v>
+      </c>
+      <c r="N7">
+        <v>0.9</v>
+      </c>
+      <c r="O7">
+        <v>0.9</v>
+      </c>
+      <c r="P7">
+        <v>0.9</v>
+      </c>
+      <c r="Q7">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>4</v>
       </c>
@@ -555,8 +894,44 @@
       <c r="E8">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F8">
+        <v>0.8</v>
+      </c>
+      <c r="G8">
+        <v>0.8</v>
+      </c>
+      <c r="H8">
+        <v>0.8</v>
+      </c>
+      <c r="I8">
+        <v>0.8</v>
+      </c>
+      <c r="J8">
+        <v>0.8</v>
+      </c>
+      <c r="K8">
+        <v>0.8</v>
+      </c>
+      <c r="L8">
+        <v>0.8</v>
+      </c>
+      <c r="M8">
+        <v>0.8</v>
+      </c>
+      <c r="N8">
+        <v>0.8</v>
+      </c>
+      <c r="O8">
+        <v>0.8</v>
+      </c>
+      <c r="P8">
+        <v>0.8</v>
+      </c>
+      <c r="Q8">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>5</v>
       </c>
@@ -572,8 +947,44 @@
       <c r="E9">
         <v>0.75</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F9">
+        <v>0.75</v>
+      </c>
+      <c r="G9">
+        <v>0.75</v>
+      </c>
+      <c r="H9">
+        <v>0.75</v>
+      </c>
+      <c r="I9">
+        <v>0.75</v>
+      </c>
+      <c r="J9">
+        <v>0.75</v>
+      </c>
+      <c r="K9">
+        <v>0.75</v>
+      </c>
+      <c r="L9">
+        <v>0.75</v>
+      </c>
+      <c r="M9">
+        <v>0.75</v>
+      </c>
+      <c r="N9">
+        <v>0.75</v>
+      </c>
+      <c r="O9">
+        <v>0.75</v>
+      </c>
+      <c r="P9">
+        <v>0.75</v>
+      </c>
+      <c r="Q9">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>6</v>
       </c>
@@ -589,8 +1000,44 @@
       <c r="E10">
         <v>0.9</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F10">
+        <v>0.9</v>
+      </c>
+      <c r="G10">
+        <v>0.9</v>
+      </c>
+      <c r="H10">
+        <v>0.9</v>
+      </c>
+      <c r="I10">
+        <v>0.9</v>
+      </c>
+      <c r="J10">
+        <v>0.9</v>
+      </c>
+      <c r="K10">
+        <v>0.9</v>
+      </c>
+      <c r="L10">
+        <v>0.9</v>
+      </c>
+      <c r="M10">
+        <v>0.9</v>
+      </c>
+      <c r="N10">
+        <v>0.9</v>
+      </c>
+      <c r="O10">
+        <v>0.9</v>
+      </c>
+      <c r="P10">
+        <v>0.9</v>
+      </c>
+      <c r="Q10">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>7</v>
       </c>
@@ -606,8 +1053,44 @@
       <c r="E11">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F11">
+        <v>0.8</v>
+      </c>
+      <c r="G11">
+        <v>0.8</v>
+      </c>
+      <c r="H11">
+        <v>0.8</v>
+      </c>
+      <c r="I11">
+        <v>0.8</v>
+      </c>
+      <c r="J11">
+        <v>0.8</v>
+      </c>
+      <c r="K11">
+        <v>0.8</v>
+      </c>
+      <c r="L11">
+        <v>0.8</v>
+      </c>
+      <c r="M11">
+        <v>0.8</v>
+      </c>
+      <c r="N11">
+        <v>0.8</v>
+      </c>
+      <c r="O11">
+        <v>0.8</v>
+      </c>
+      <c r="P11">
+        <v>0.8</v>
+      </c>
+      <c r="Q11">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>8</v>
       </c>
@@ -623,8 +1106,44 @@
       <c r="E12">
         <v>0.75</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F12">
+        <v>0.75</v>
+      </c>
+      <c r="G12">
+        <v>0.75</v>
+      </c>
+      <c r="H12">
+        <v>0.75</v>
+      </c>
+      <c r="I12">
+        <v>0.75</v>
+      </c>
+      <c r="J12">
+        <v>0.75</v>
+      </c>
+      <c r="K12">
+        <v>0.75</v>
+      </c>
+      <c r="L12">
+        <v>0.75</v>
+      </c>
+      <c r="M12">
+        <v>0.75</v>
+      </c>
+      <c r="N12">
+        <v>0.75</v>
+      </c>
+      <c r="O12">
+        <v>0.75</v>
+      </c>
+      <c r="P12">
+        <v>0.75</v>
+      </c>
+      <c r="Q12">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <v>9</v>
       </c>
@@ -640,8 +1159,44 @@
       <c r="E13">
         <v>0.8</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F13">
+        <v>0.8</v>
+      </c>
+      <c r="G13">
+        <v>0.8</v>
+      </c>
+      <c r="H13">
+        <v>0.8</v>
+      </c>
+      <c r="I13">
+        <v>0.8</v>
+      </c>
+      <c r="J13">
+        <v>0.8</v>
+      </c>
+      <c r="K13">
+        <v>0.8</v>
+      </c>
+      <c r="L13">
+        <v>0.8</v>
+      </c>
+      <c r="M13">
+        <v>0.8</v>
+      </c>
+      <c r="N13">
+        <v>0.8</v>
+      </c>
+      <c r="O13">
+        <v>0.8</v>
+      </c>
+      <c r="P13">
+        <v>0.8</v>
+      </c>
+      <c r="Q13">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>10</v>
       </c>
@@ -657,8 +1212,44 @@
       <c r="E14">
         <v>0.75</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F14">
+        <v>0.75</v>
+      </c>
+      <c r="G14">
+        <v>0.75</v>
+      </c>
+      <c r="H14">
+        <v>0.75</v>
+      </c>
+      <c r="I14">
+        <v>0.75</v>
+      </c>
+      <c r="J14">
+        <v>0.75</v>
+      </c>
+      <c r="K14">
+        <v>0.75</v>
+      </c>
+      <c r="L14">
+        <v>0.75</v>
+      </c>
+      <c r="M14">
+        <v>0.75</v>
+      </c>
+      <c r="N14">
+        <v>0.75</v>
+      </c>
+      <c r="O14">
+        <v>0.75</v>
+      </c>
+      <c r="P14">
+        <v>0.75</v>
+      </c>
+      <c r="Q14">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
         <v>11</v>
       </c>
@@ -672,6 +1263,42 @@
         <v>0.9</v>
       </c>
       <c r="E15">
+        <v>0.9</v>
+      </c>
+      <c r="F15">
+        <v>0.9</v>
+      </c>
+      <c r="G15">
+        <v>0.9</v>
+      </c>
+      <c r="H15">
+        <v>0.9</v>
+      </c>
+      <c r="I15">
+        <v>0.9</v>
+      </c>
+      <c r="J15">
+        <v>0.9</v>
+      </c>
+      <c r="K15">
+        <v>0.9</v>
+      </c>
+      <c r="L15">
+        <v>0.9</v>
+      </c>
+      <c r="M15">
+        <v>0.9</v>
+      </c>
+      <c r="N15">
+        <v>0.9</v>
+      </c>
+      <c r="O15">
+        <v>0.9</v>
+      </c>
+      <c r="P15">
+        <v>0.9</v>
+      </c>
+      <c r="Q15">
         <v>0.9</v>
       </c>
     </row>
